--- a/AfterToken/Configs/GameConfig/Datas/npc.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/npc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>dialogueId</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>patrolPath</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +479,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,7 +513,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>对话ID(预留,0=无)</t>
+          <t>对话ID(0=无)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>移动速度(0=站桩)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>巡逻路径(x,z|x,z)</t>
         </is>
       </c>
     </row>
@@ -512,7 +542,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3,3|4,3</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -530,8 +568,12 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>901</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AfterToken/Configs/GameConfig/Datas/npc.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/npc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>patrolPath</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>consoleType</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +534,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>巡逻路径(x,z|x,z)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>功能台类型(0=无 1=技能树)</t>
         </is>
       </c>
     </row>
@@ -552,6 +567,9 @@
           <t>-3,3|4,3</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -573,7 +591,33 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Skill Console</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tech Station</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
